--- a/data/trans_orig/IP26C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP26C-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72461</t>
+          <t>72553</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83214</t>
+          <t>83333</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74992</t>
+          <t>74907</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82994</t>
+          <t>83075</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151500</t>
+          <t>152053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164693</t>
+          <t>164874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17161</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8502</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356715</t>
+          <t>356675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377863</t>
+          <t>376993</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>415546</t>
+          <t>415573</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>435939</t>
+          <t>436908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>779738</t>
+          <t>780014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>807876</t>
+          <t>810870</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35869</t>
+          <t>36790</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56658</t>
+          <t>57001</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33674</t>
+          <t>32684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53616</t>
+          <t>53043</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>75268</t>
+          <t>72072</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>103293</t>
+          <t>102125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>458</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146398</t>
+          <t>146245</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159891</t>
+          <t>159719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>132987</t>
+          <t>134417</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>146503</t>
+          <t>146297</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>285203</t>
+          <t>284668</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>302789</t>
+          <t>303023</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12252</t>
+          <t>12067</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>25291</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>586422</t>
+          <t>586184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>613781</t>
+          <t>613347</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>633841</t>
+          <t>635457</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>660142</t>
+          <t>659996</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1229278</t>
+          <t>1229846</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1267329</t>
+          <t>1265379</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61995</t>
+          <t>62459</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89184</t>
+          <t>88973</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50237</t>
+          <t>50782</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75519</t>
+          <t>73742</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118599</t>
+          <t>119561</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>155570</t>
+          <t>154357</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16963</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75315</t>
+          <t>75481</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85881</t>
+          <t>85999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>65204</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76776</t>
+          <t>76679</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144498</t>
+          <t>144432</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160631</t>
+          <t>159375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>14739</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16012</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>30824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385418</t>
+          <t>385202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407733</t>
+          <t>408096</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426176</t>
+          <t>427021</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447698</t>
+          <t>447891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>819840</t>
+          <t>820675</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>851672</t>
+          <t>852024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38318</t>
+          <t>37573</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60365</t>
+          <t>59281</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36241</t>
+          <t>34743</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56105</t>
+          <t>56017</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,47 +3407,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>93068</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>77866</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>107558</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>9,95%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>11,5%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>93068</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>78816</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>109022</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>9,95%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>145232</t>
+          <t>144681</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156578</t>
+          <t>156129</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146540</t>
+          <t>145768</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159130</t>
+          <t>159123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>295220</t>
+          <t>295506</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>313147</t>
+          <t>312425</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>19158</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36612</t>
+          <t>35754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>616043</t>
+          <t>615872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>641650</t>
+          <t>641884</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>647817</t>
+          <t>648615</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>675478</t>
+          <t>676646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1274259</t>
+          <t>1272291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1313178</t>
+          <t>1311356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57540</t>
+          <t>57658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82091</t>
+          <t>83816</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61979</t>
+          <t>61386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87596</t>
+          <t>87584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124233</t>
+          <t>125898</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>160998</t>
+          <t>162892</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18310</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49265</t>
+          <t>49007</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56288</t>
+          <t>56294</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58882</t>
+          <t>58540</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66523</t>
+          <t>66461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111420</t>
+          <t>111403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121417</t>
+          <t>121659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>550</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411707</t>
+          <t>411466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>432918</t>
+          <t>433060</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>425197</t>
+          <t>425258</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446926</t>
+          <t>447277</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>843332</t>
+          <t>844212</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>874321</t>
+          <t>873867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31910</t>
+          <t>31971</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52564</t>
+          <t>52679</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35135</t>
+          <t>34918</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56712</t>
+          <t>56369</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>71225</t>
+          <t>73395</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>101157</t>
+          <t>102073</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,47 +5540,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2147</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6420</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2147</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5772</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9623</t>
+          <t>9452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146516</t>
+          <t>146975</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>160260</t>
+          <t>159925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,49 +5770,49 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>93,78%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>169270</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>162163</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>174927</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>90,93%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>87,11%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t>93,97%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>169270</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>162143</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>175347</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>90,93%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>87,1%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>476</t>
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>313450</t>
+          <t>313264</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>331711</t>
+          <t>331634</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>21470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>22743</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>21905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40092</t>
+          <t>40062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>618748</t>
+          <t>618171</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>643814</t>
+          <t>643296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>654697</t>
+          <t>655990</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>682042</t>
+          <t>683063</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1282914</t>
+          <t>1283267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1318549</t>
+          <t>1318282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47347</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70655</t>
+          <t>73036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79651</t>
+          <t>78598</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108232</t>
+          <t>108170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142180</t>
+          <t>142307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46276</t>
+          <t>46300</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53065</t>
+          <t>53025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47346</t>
+          <t>47221</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57647</t>
+          <t>57559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96843</t>
+          <t>96516</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108729</t>
+          <t>108977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19839</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403920</t>
+          <t>403206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>426574</t>
+          <t>426090</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>451021</t>
+          <t>450783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476202</t>
+          <t>475821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>861128</t>
+          <t>862823</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>894485</t>
+          <t>896182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51164</t>
+          <t>51831</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37231</t>
+          <t>37460</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62751</t>
+          <t>62665</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>75329</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108400</t>
+          <t>105559</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>131251</t>
+          <t>131204</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141934</t>
+          <t>141960</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>153019</t>
+          <t>152929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>168566</t>
+          <t>168096</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>288945</t>
+          <t>287878</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>306812</t>
+          <t>307135</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16871</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>12896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27456</t>
+          <t>27918</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>22286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>41600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>588912</t>
+          <t>589172</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>614707</t>
+          <t>615256</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>662807</t>
+          <t>662358</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>694049</t>
+          <t>694501</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1259292</t>
+          <t>1259625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1300985</t>
+          <t>1302322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44281</t>
+          <t>43519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69793</t>
+          <t>69089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61217</t>
+          <t>62606</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93255</t>
+          <t>94050</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>114470</t>
+          <t>112201</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154136</t>
+          <t>154975</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,49 +8507,49 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>5420</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2627</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>5420</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2522</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>9965</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>19</t>
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP26C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP26C-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>80345</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>75337</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>83475</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>93,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>87,46%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>78620</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>72553</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>83333</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>72558</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>83309</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>86,52%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>79,85%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>80345</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>74907</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>83075</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>93,27%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>86,96%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>152053</t>
+          <t>151782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164874</t>
+          <t>164777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4469</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1916</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8394</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11374</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6880</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17440</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6687</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17029</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>12,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4469</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1946</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9050</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22381</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>873</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4630</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4685</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4871</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86141</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86141</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86141</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86141</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86141</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86141</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>426796</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>415581</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>436511</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>556</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>367822</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>356675</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>376993</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>356378</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>376806</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>426796</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>415573</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>436908</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>780014</t>
+          <t>778258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>810870</t>
+          <t>808947</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>42572</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>33648</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>54419</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11,51%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>45727</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>36790</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>57001</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>36818</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>56893</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>11,01%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>8,86%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>42572</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>32684</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>53043</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>72072</t>
+          <t>74793</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>102125</t>
+          <t>103582</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3516</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7191</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1916</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>458</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5430</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5924</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3516</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1322</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7707</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>472883</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>472883</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>472883</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>415465</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>415465</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>415465</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>472883</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>472883</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>472883</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1635,74 +1635,74 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141089</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>133901</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>146526</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>89,98%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>85,39%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>153680</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146245</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>159719</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>146234</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>159733</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>88,99%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>84,68%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>92,49%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141089</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>134417</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>146297</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>89,98%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>85,72%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>93,3%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>435</t>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>284668</t>
+          <t>284631</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>303023</t>
+          <t>303051</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14312</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9149</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20887</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>17801</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12067</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25291</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12073</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24775</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,31%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>6,99%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14312</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9518</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20971</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42071</t>
+          <t>42295</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -1866,67 +1866,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4675</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>1216</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4217</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4585</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4967</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>156805</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>156805</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156805</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172697</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172697</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172697</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>156805</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>156805</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>156805</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,72 +2091,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>648228</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>635340</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>659556</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>90,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>898</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>600121</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>586184</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>613347</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>585058</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>613134</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>88,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>86,33%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>648228</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>635457</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>659996</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>90,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1229846</t>
+          <t>1228776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1265379</t>
+          <t>1265480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>61352</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>50385</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>73769</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>74903</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>62459</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>88973</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>61912</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>88792</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>11,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>61352</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>50782</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>73742</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119561</t>
+          <t>119870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154357</t>
+          <t>155528</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -2317,74 +2317,74 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6248</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3210</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11830</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>4005</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1657</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8395</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1539</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8420</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>6248</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>3026</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>11552</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>16</t>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>15803</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1076</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>715828</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>715828</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>715828</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>679029</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>679029</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>679029</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>715828</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>715828</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>715828</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>71686</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>65636</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>76600</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>88,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>81370</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>75481</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>85999</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>75121</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>85678</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>88,09%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>71686</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>65204</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>76679</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>83,17%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144432</t>
+          <t>144899</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159375</t>
+          <t>159871</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13283</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8346</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19511</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9299</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5103</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14739</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5074</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14540</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>10,07%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13283</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8579</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19652</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>15,41%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16618</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30824</t>
+          <t>30670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -3009,67 +3009,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>1223</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>1700</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5440</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5810</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4305</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>941</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>438213</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>426951</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>448169</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,53%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>578</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>397524</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>385202</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>408096</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>386264</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>408296</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>438213</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>427021</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>447891</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,84%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>820675</t>
+          <t>821288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>852024</t>
+          <t>850279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>44992</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35931</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>55157</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>48076</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>37573</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>59281</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>37722</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>59357</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>10,73%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>44992</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>34743</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>56017</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>77866</t>
+          <t>78998</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>107558</t>
+          <t>108045</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4585</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9458</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2290</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5750</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6751</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4585</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9202</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>12382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>487790</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>487790</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>487790</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>447890</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>447890</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>447890</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>487790</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>487790</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>487790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>153151</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>146407</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158567</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>89,9%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>85,94%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>93,08%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>151464</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>144681</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>156129</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>145474</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>156565</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>92,74%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>88,59%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>153151</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>145768</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>159123</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>89,9%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>295506</t>
+          <t>295404</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>312425</t>
+          <t>311588</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15072</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21708</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11854</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7189</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18637</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6753</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17844</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,26%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15072</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9529</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>22006</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35754</t>
+          <t>36882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -3916,92 +3916,92 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2128</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5446</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>2128</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5560</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6547</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170351</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170351</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170351</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>163318</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>163318</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>163318</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170351</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170351</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170351</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>663050</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>648330</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>676086</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>87,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>912</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>630359</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>615872</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>641884</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>616751</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>643375</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>89,59%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>663050</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>648615</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>676646</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>89,08%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1272291</t>
+          <t>1273041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1311356</t>
+          <t>1312165</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -4259,107 +4259,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>73347</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>60818</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>87043</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>69229</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>57658</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>83816</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>56705</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>82923</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>9,84%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>73347</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>61386</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>87584</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>8,06%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>11,79%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>142576</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>124827</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>161418</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>9,85%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>142576</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>125898</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>162892</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7936</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4028</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13032</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3990</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1493</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9551</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>9214</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7936</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4458</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13396</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>744333</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>744333</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>744333</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>703577</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>703577</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>703577</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>744333</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>744333</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>744333</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4833,72 +4833,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>63554</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>58870</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66470</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>92,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>53714</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>49007</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>56294</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>49566</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>56453</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>91,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>83,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>63554</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>58540</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66461</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111403</t>
+          <t>111317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121659</t>
+          <t>121685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -4946,72 +4946,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5060</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2144</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9744</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3236</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7381</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1173</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>5,5%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5060</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2153</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10074</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13949</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -5059,72 +5059,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1864</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5054</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4653</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,17%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>556</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>58814</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>58814</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>58814</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5289,74 +5289,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>437069</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>424883</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>446557</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>423305</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>411466</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>433060</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>412612</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>433059</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>88,24%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>92,62%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>437069</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>425258</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>447277</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,35%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>87,9%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1263</t>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>844212</t>
+          <t>844085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>873867</t>
+          <t>873783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5402,72 +5402,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>44558</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35128</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56119</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41543</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31971</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>52679</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>31914</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>51966</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>8,88%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>44558</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>34918</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>56369</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>73395</t>
+          <t>72611</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>102073</t>
+          <t>102959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -5515,64 +5515,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2147</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6436</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2737</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6634</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7006</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2147</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6420</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,15%</t>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>483774</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>483774</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>483774</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>706</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>467585</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>467585</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>467585</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>483774</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>483774</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>483774</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5745,72 +5745,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>169270</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>162127</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>174560</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>90,93%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>87,09%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154378</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146975</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>159925</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>147242</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>160160</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>90,52%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>86,18%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>169270</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>162163</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>174927</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>90,93%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>313264</t>
+          <t>313659</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>331634</t>
+          <t>331868</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15806</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10904</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22759</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>14278</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9194</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>21470</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8937</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21101</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15806</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10390</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>22743</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>22744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40062</t>
+          <t>39791</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -5971,72 +5971,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5403</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1881</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5343</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5393</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4699</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186157</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186157</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186157</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170538</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170538</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170538</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186157</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186157</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186157</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>669894</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>656226</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>682121</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>90,7%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>952</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>631399</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>618171</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>643296</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>618325</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>644012</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>90,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>669894</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>655990</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>683063</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1283267</t>
+          <t>1282111</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1318282</t>
+          <t>1318400</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6314,72 +6314,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>65424</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>53430</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>78828</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8,86%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>59057</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>48049</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>73036</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>46922</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>71334</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>8,47%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>65424</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>52859</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>78598</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>8,86%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108170</t>
+          <t>108812</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142307</t>
+          <t>142987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8265</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>6482</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3007</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>11709</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>12055</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3228</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1084</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>8417</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15697</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1056</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>738546</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>738546</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>738546</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1049</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>696938</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>696938</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>696938</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1056</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>738546</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>738546</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>738546</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6888,72 +6888,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47853</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42246</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51962</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>74,47%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>50547</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>46300</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53025</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>92,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>53217</t>
+          <t>42422</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47221</t>
+          <t>38501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57559</t>
+          <t>44994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>103764</t>
+          <t>90275</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96516</t>
+          <t>83305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108977</t>
+          <t>95372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -7001,72 +7001,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8879</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4770</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14486</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4131</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1653</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8378</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>20185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>425452</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>412216</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>436233</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>575</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>415300</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>403206</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>426090</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>90,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>463808</t>
+          <t>386890</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450783</t>
+          <t>375520</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>475821</t>
+          <t>396525</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>879108</t>
+          <t>812342</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>862823</t>
+          <t>795939</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>896182</t>
+          <t>828435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -7457,72 +7457,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47601</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37245</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>60856</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>40228</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30126</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>51831</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>40261</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37460</t>
+          <t>31156</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62665</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>89964</t>
+          <t>87862</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>73240</t>
+          <t>71524</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>105559</t>
+          <t>103819</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -7575,67 +7575,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6358</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3235</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>1107</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6900</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475321</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475321</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475321</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>458504</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>458504</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>458504</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>516192</t>
+          <t>430386</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516192</t>
+          <t>430386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516192</t>
+          <t>430386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>974697</t>
+          <t>905707</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>974697</t>
+          <t>905707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>974697</t>
+          <t>905707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7800,72 +7800,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>148051</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>140102</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>154993</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>83,19%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>137167</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>131204</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>141960</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>91,72%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>87,73%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>161724</t>
+          <t>137032</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>152929</t>
+          <t>130705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>168096</t>
+          <t>141624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>298891</t>
+          <t>285083</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>287878</t>
+          <t>275751</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>307135</t>
+          <t>293719</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -7913,72 +7913,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18237</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11807</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26440</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11109</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6585</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16896</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12896</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27918</t>
+          <t>17850</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>29962</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22286</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41600</t>
+          <t>39023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2131</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5015</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3788</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>621356</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>605976</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>636516</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>88,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>845</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>603014</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>589172</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>615256</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>90,99%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88,9%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,84%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>678749</t>
+          <t>566344</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>662358</t>
+          <t>553243</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>694501</t>
+          <t>578361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1281763</t>
+          <t>1187700</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1259625</t>
+          <t>1166785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1302322</t>
+          <t>1205146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -8369,72 +8369,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>74717</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>60198</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>90247</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>55468</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>43519</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>69089</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>77376</t>
+          <t>55952</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62606</t>
+          <t>44478</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94050</t>
+          <t>67568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>132843</t>
+          <t>130669</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112201</t>
+          <t>114140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154975</t>
+          <t>150911</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -8482,72 +8482,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4399</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2188</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8874</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>4252</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8306</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -8595,57 +8595,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>700472</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>700472</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>700472</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>662733</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>662733</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>662733</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>761545</t>
+          <t>627120</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>761545</t>
+          <t>627120</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>761545</t>
+          <t>627120</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1424278</t>
+          <t>1327592</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1424278</t>
+          <t>1327592</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1424278</t>
+          <t>1327592</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
